--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/45.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/45.xlsx
@@ -426,13 +426,13 @@
         <v>-13.7171980267397</v>
       </c>
       <c r="E2">
-        <v>-15.05016807444767</v>
+        <v>-16.73463813650283</v>
       </c>
       <c r="F2">
-        <v>-0.5380396859790371</v>
+        <v>-1.255236041485835</v>
       </c>
       <c r="G2">
-        <v>-10.74712776171611</v>
+        <v>-12.71149292617129</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.27084458906088</v>
       </c>
       <c r="E3">
-        <v>-15.93241896604403</v>
+        <v>-17.00857005770082</v>
       </c>
       <c r="F3">
-        <v>-0.6002939814016283</v>
+        <v>-1.223016691353948</v>
       </c>
       <c r="G3">
-        <v>-9.941390635640587</v>
+        <v>-12.43220206229622</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.75634282447398</v>
       </c>
       <c r="E4">
-        <v>-16.24216658816868</v>
+        <v>-17.96192704816562</v>
       </c>
       <c r="F4">
-        <v>-0.6045493047498094</v>
+        <v>-1.157861453286753</v>
       </c>
       <c r="G4">
-        <v>-10.2007983630068</v>
+        <v>-11.98581141232643</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.23826665868689</v>
       </c>
       <c r="E5">
-        <v>-17.19378011614053</v>
+        <v>-20.08417827796431</v>
       </c>
       <c r="F5">
-        <v>-0.4594532988428507</v>
+        <v>-1.643893601368321</v>
       </c>
       <c r="G5">
-        <v>-10.13654729518063</v>
+        <v>-12.03016279091605</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.7033980807196</v>
       </c>
       <c r="E6">
-        <v>-18.10013607487972</v>
+        <v>-19.73935762465025</v>
       </c>
       <c r="F6">
-        <v>-0.509998621026871</v>
+        <v>-1.45927370157159</v>
       </c>
       <c r="G6">
-        <v>-9.139430842025378</v>
+        <v>-12.23719768785099</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.17471671638694</v>
       </c>
       <c r="E7">
-        <v>-17.84138359855545</v>
+        <v>-20.02046264867638</v>
       </c>
       <c r="F7">
-        <v>-0.7486885463065345</v>
+        <v>-1.364419007011824</v>
       </c>
       <c r="G7">
-        <v>-8.691004206548939</v>
+        <v>-12.05005254851599</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.65043712713599</v>
       </c>
       <c r="E8">
-        <v>-17.84545922516235</v>
+        <v>-21.06957422203337</v>
       </c>
       <c r="F8">
-        <v>-0.6554723624695061</v>
+        <v>-1.13415026474902</v>
       </c>
       <c r="G8">
-        <v>-8.433990003607621</v>
+        <v>-11.32658247909136</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.13701202990865</v>
       </c>
       <c r="E9">
-        <v>-19.43056551054121</v>
+        <v>-21.95335573784433</v>
       </c>
       <c r="F9">
-        <v>-0.5606334068903935</v>
+        <v>-0.6983693684234785</v>
       </c>
       <c r="G9">
-        <v>-8.409250296792647</v>
+        <v>-10.72010708902457</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.636292138951886</v>
       </c>
       <c r="E10">
-        <v>-20.88175123409124</v>
+        <v>-22.24554646624124</v>
       </c>
       <c r="F10">
-        <v>-0.9112241711446312</v>
+        <v>-1.253080629503751</v>
       </c>
       <c r="G10">
-        <v>-7.832592990398077</v>
+        <v>-10.32640708185783</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.140580328580818</v>
       </c>
       <c r="E11">
-        <v>-21.64272506328818</v>
+        <v>-22.32378491167177</v>
       </c>
       <c r="F11">
-        <v>-0.6294309764276981</v>
+        <v>-1.155484867208121</v>
       </c>
       <c r="G11">
-        <v>-7.035459972179125</v>
+        <v>-9.156404009005222</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.656791704060945</v>
       </c>
       <c r="E12">
-        <v>-22.01993789117911</v>
+        <v>-24.07525374667041</v>
       </c>
       <c r="F12">
-        <v>-0.3288512373826751</v>
+        <v>-0.9606652795807196</v>
       </c>
       <c r="G12">
-        <v>-6.853323688245043</v>
+        <v>-9.06129203566196</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.168986089283294</v>
       </c>
       <c r="E13">
-        <v>-21.84604448928457</v>
+        <v>-24.800593013901</v>
       </c>
       <c r="F13">
-        <v>-0.5036674089672744</v>
+        <v>-0.6636193558760393</v>
       </c>
       <c r="G13">
-        <v>-6.356976906087652</v>
+        <v>-8.863119469135649</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.690153890923328</v>
       </c>
       <c r="E14">
-        <v>-22.5041676168193</v>
+        <v>-25.85870266511123</v>
       </c>
       <c r="F14">
-        <v>-0.2598175831355727</v>
+        <v>-0.6368167001910585</v>
       </c>
       <c r="G14">
-        <v>-6.184964270412661</v>
+        <v>-8.26879047065245</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.205770561278601</v>
       </c>
       <c r="E15">
-        <v>-23.22769549444681</v>
+        <v>-26.00482293591673</v>
       </c>
       <c r="F15">
-        <v>-0.2708141604077361</v>
+        <v>-0.8087443546420959</v>
       </c>
       <c r="G15">
-        <v>-5.127059580065318</v>
+        <v>-8.140198950270538</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.726814009441117</v>
       </c>
       <c r="E16">
-        <v>-23.14893627450541</v>
+        <v>-27.1358093193324</v>
       </c>
       <c r="F16">
-        <v>-0.09913253107533018</v>
+        <v>-0.09987309153343295</v>
       </c>
       <c r="G16">
-        <v>-5.214160033203543</v>
+        <v>-7.859693116182552</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.24490653637551</v>
       </c>
       <c r="E17">
-        <v>-25.22716620847553</v>
+        <v>-26.97131250100378</v>
       </c>
       <c r="F17">
-        <v>0.001166194055633952</v>
+        <v>-0.206059852163496</v>
       </c>
       <c r="G17">
-        <v>-4.814550702249196</v>
+        <v>-7.056766643269874</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.769124050639926</v>
       </c>
       <c r="E18">
-        <v>-25.34358421826472</v>
+        <v>-27.23789018041331</v>
       </c>
       <c r="F18">
-        <v>0.3190687522280002</v>
+        <v>-0.01665447388079181</v>
       </c>
       <c r="G18">
-        <v>-4.817275281228016</v>
+        <v>-7.394981907198437</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.301531763589963</v>
       </c>
       <c r="E19">
-        <v>-25.77230843799289</v>
+        <v>-28.38225367604764</v>
       </c>
       <c r="F19">
-        <v>0.6988768631463791</v>
+        <v>0.05500179156357382</v>
       </c>
       <c r="G19">
-        <v>-4.685108371663692</v>
+        <v>-6.895927098789923</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.85263995272199</v>
       </c>
       <c r="E20">
-        <v>-26.96571077865629</v>
+        <v>-29.06331805290523</v>
       </c>
       <c r="F20">
-        <v>1.064164521861086</v>
+        <v>0.2807145131109803</v>
       </c>
       <c r="G20">
-        <v>-4.648261999811605</v>
+        <v>-6.532091522932942</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.436456561048613</v>
       </c>
       <c r="E21">
-        <v>-27.3469901762061</v>
+        <v>-29.56282005713629</v>
       </c>
       <c r="F21">
-        <v>1.340486349882528</v>
+        <v>0.9416456695174275</v>
       </c>
       <c r="G21">
-        <v>-3.953232827114854</v>
+        <v>-6.77961439181317</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.06322362000452</v>
       </c>
       <c r="E22">
-        <v>-27.34236660424427</v>
+        <v>-30.36222478099932</v>
       </c>
       <c r="F22">
-        <v>1.396136072002599</v>
+        <v>1.163053365672485</v>
       </c>
       <c r="G22">
-        <v>-5.021377034815163</v>
+        <v>-6.64579552002475</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.756170591226612</v>
       </c>
       <c r="E23">
-        <v>-26.92107813883669</v>
+        <v>-30.51182065560571</v>
       </c>
       <c r="F23">
-        <v>1.902808650659722</v>
+        <v>0.85837486471841</v>
       </c>
       <c r="G23">
-        <v>-3.888776505465244</v>
+        <v>-5.828478105652861</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.522227745426965</v>
       </c>
       <c r="E24">
-        <v>-29.1586514877147</v>
+        <v>-30.09767812218223</v>
       </c>
       <c r="F24">
-        <v>1.968847756745704</v>
+        <v>1.309801964548029</v>
       </c>
       <c r="G24">
-        <v>-4.313287759965989</v>
+        <v>-6.155771879847368</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.387341755068373</v>
       </c>
       <c r="E25">
-        <v>-28.5399849542088</v>
+        <v>-30.50570947993236</v>
       </c>
       <c r="F25">
-        <v>2.073285005421055</v>
+        <v>1.347784266701191</v>
       </c>
       <c r="G25">
-        <v>-4.234695408863691</v>
+        <v>-6.761436186257032</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.351435521308028</v>
       </c>
       <c r="E26">
-        <v>-28.79913593624575</v>
+        <v>-29.99827132500286</v>
       </c>
       <c r="F26">
-        <v>2.52724690950324</v>
+        <v>1.189928917688912</v>
       </c>
       <c r="G26">
-        <v>-3.758625718134337</v>
+        <v>-6.492696031015615</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.431696779161481</v>
       </c>
       <c r="E27">
-        <v>-28.34324087247156</v>
+        <v>-31.73145418195853</v>
       </c>
       <c r="F27">
-        <v>2.034394812594423</v>
+        <v>1.453348095044349</v>
       </c>
       <c r="G27">
-        <v>-4.741162528734632</v>
+        <v>-6.871402577435003</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.619556262554125</v>
       </c>
       <c r="E28">
-        <v>-28.98226742511594</v>
+        <v>-31.03515601853914</v>
       </c>
       <c r="F28">
-        <v>2.305545971287591</v>
+        <v>1.25371486443928</v>
       </c>
       <c r="G28">
-        <v>-4.747300280164441</v>
+        <v>-6.5918733542811</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.914517203220357</v>
       </c>
       <c r="E29">
-        <v>-28.3466915696654</v>
+        <v>-31.18287031219534</v>
       </c>
       <c r="F29">
-        <v>2.351967680540475</v>
+        <v>1.524188418596957</v>
       </c>
       <c r="G29">
-        <v>-4.727857446212302</v>
+        <v>-6.117657569053739</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.298065588527002</v>
       </c>
       <c r="E30">
-        <v>-28.05990331075964</v>
+        <v>-30.0655984123119</v>
       </c>
       <c r="F30">
-        <v>2.103656267877295</v>
+        <v>1.409862119866987</v>
       </c>
       <c r="G30">
-        <v>-5.201709071430344</v>
+        <v>-7.249360940562515</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.750270166654707</v>
       </c>
       <c r="E31">
-        <v>-28.48770372179025</v>
+        <v>-30.38291764297737</v>
       </c>
       <c r="F31">
-        <v>2.209172050911091</v>
+        <v>1.200863367405866</v>
       </c>
       <c r="G31">
-        <v>-5.502276811486314</v>
+        <v>-7.130472629156208</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.247206215396858</v>
       </c>
       <c r="E32">
-        <v>-28.61197410550874</v>
+        <v>-29.81030116165547</v>
       </c>
       <c r="F32">
-        <v>2.137210117895092</v>
+        <v>1.154007593633914</v>
       </c>
       <c r="G32">
-        <v>-5.247523711148317</v>
+        <v>-6.943102372724538</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.75866263230912</v>
       </c>
       <c r="E33">
-        <v>-28.10130262013776</v>
+        <v>-30.04316208784089</v>
       </c>
       <c r="F33">
-        <v>1.905316947155399</v>
+        <v>1.029644795451625</v>
       </c>
       <c r="G33">
-        <v>-6.083039194349579</v>
+        <v>-6.562780280081985</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.261785420911536</v>
       </c>
       <c r="E34">
-        <v>-26.74767381213497</v>
+        <v>-30.0306499141577</v>
       </c>
       <c r="F34">
-        <v>2.241375662062325</v>
+        <v>1.131797406830054</v>
       </c>
       <c r="G34">
-        <v>-5.750604142932585</v>
+        <v>-6.970636179974656</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.721570778686843</v>
       </c>
       <c r="E35">
-        <v>-26.24883975782005</v>
+        <v>-28.94453165121003</v>
       </c>
       <c r="F35">
-        <v>2.232450831664563</v>
+        <v>1.203111556537063</v>
       </c>
       <c r="G35">
-        <v>-5.962717416724768</v>
+        <v>-7.199020785092357</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.120232646180018</v>
       </c>
       <c r="E36">
-        <v>-26.8436865180456</v>
+        <v>-28.86432331958617</v>
       </c>
       <c r="F36">
-        <v>1.89665056738731</v>
+        <v>1.18884541312605</v>
       </c>
       <c r="G36">
-        <v>-6.27195547554809</v>
+        <v>-7.942638834668991</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.430065400856765</v>
       </c>
       <c r="E37">
-        <v>-25.59168572372295</v>
+        <v>-28.6667414701575</v>
       </c>
       <c r="F37">
-        <v>1.758692603390275</v>
+        <v>0.9419521654564633</v>
       </c>
       <c r="G37">
-        <v>-6.251638657573583</v>
+        <v>-7.864506649396652</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.645769021187038</v>
       </c>
       <c r="E38">
-        <v>-25.07431662529463</v>
+        <v>-27.39397309403568</v>
       </c>
       <c r="F38">
-        <v>1.895235715863329</v>
+        <v>1.140316337200444</v>
       </c>
       <c r="G38">
-        <v>-6.333975235680796</v>
+        <v>-7.90394186786045</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.754359553819196</v>
       </c>
       <c r="E39">
-        <v>-24.69199567872305</v>
+        <v>-27.2025227984134</v>
       </c>
       <c r="F39">
-        <v>1.47105196317698</v>
+        <v>1.261617489461987</v>
       </c>
       <c r="G39">
-        <v>-5.898244542347462</v>
+        <v>-8.227236503043518</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.760246297118194</v>
       </c>
       <c r="E40">
-        <v>-23.3876230825017</v>
+        <v>-27.67420865105235</v>
       </c>
       <c r="F40">
-        <v>1.586692052607791</v>
+        <v>1.067383557588364</v>
       </c>
       <c r="G40">
-        <v>-5.25332378693312</v>
+        <v>-7.603526412899286</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.665297993881607</v>
       </c>
       <c r="E41">
-        <v>-23.88151204320025</v>
+        <v>-26.22294141497018</v>
       </c>
       <c r="F41">
-        <v>1.830762224168638</v>
+        <v>0.7473222739643026</v>
       </c>
       <c r="G41">
-        <v>-6.06328185857121</v>
+        <v>-7.615371544838799</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.481858099926757</v>
       </c>
       <c r="E42">
-        <v>-22.61180944398162</v>
+        <v>-26.47083008215006</v>
       </c>
       <c r="F42">
-        <v>1.394868669876315</v>
+        <v>0.7964212666630349</v>
       </c>
       <c r="G42">
-        <v>-5.983510953256931</v>
+        <v>-7.255422549444921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.227027934315484</v>
       </c>
       <c r="E43">
-        <v>-23.24498973668211</v>
+        <v>-25.24235923877126</v>
       </c>
       <c r="F43">
-        <v>1.611788271443005</v>
+        <v>0.9292035911273789</v>
       </c>
       <c r="G43">
-        <v>-5.084644870616176</v>
+        <v>-7.877202591539756</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.919864253689616</v>
       </c>
       <c r="E44">
-        <v>-22.90431263708507</v>
+        <v>-25.69865280825814</v>
       </c>
       <c r="F44">
-        <v>1.459115188902639</v>
+        <v>0.7721666691090654</v>
       </c>
       <c r="G44">
-        <v>-5.749958586552427</v>
+        <v>-6.921494441989715</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.588343967351746</v>
       </c>
       <c r="E45">
-        <v>-21.80094994511618</v>
+        <v>-23.45681363686489</v>
       </c>
       <c r="F45">
-        <v>1.09549834723938</v>
+        <v>0.5646357836857052</v>
       </c>
       <c r="G45">
-        <v>-5.760376873364514</v>
+        <v>-7.778521850105161</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.248557291417241</v>
       </c>
       <c r="E46">
-        <v>-20.79777974056701</v>
+        <v>-24.22662704732481</v>
       </c>
       <c r="F46">
-        <v>1.233057038148266</v>
+        <v>0.754472741385268</v>
       </c>
       <c r="G46">
-        <v>-4.987404216491163</v>
+        <v>-6.899363445059687</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.928811946377611</v>
       </c>
       <c r="E47">
-        <v>-19.97854709326139</v>
+        <v>-24.2419106471007</v>
       </c>
       <c r="F47">
-        <v>0.6310310877548913</v>
+        <v>0.5446307109080972</v>
       </c>
       <c r="G47">
-        <v>-5.029064121557351</v>
+        <v>-7.404718221629434</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.634839322998481</v>
       </c>
       <c r="E48">
-        <v>-19.79072410531925</v>
+        <v>-23.04055630607984</v>
       </c>
       <c r="F48">
-        <v>0.8789796754956448</v>
+        <v>0.5460588163105236</v>
       </c>
       <c r="G48">
-        <v>-4.584990853465054</v>
+        <v>-6.786053402887052</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.385570432787489</v>
       </c>
       <c r="E49">
-        <v>-19.59844057047956</v>
+        <v>-22.41221242361954</v>
       </c>
       <c r="F49">
-        <v>0.7492556834824367</v>
+        <v>0.3340580603816573</v>
       </c>
       <c r="G49">
-        <v>-4.706140267474683</v>
+        <v>-7.070283600706719</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.176469776186419</v>
       </c>
       <c r="E50">
-        <v>-20.27176578525804</v>
+        <v>-21.57790448634239</v>
       </c>
       <c r="F50">
-        <v>0.6561297916923134</v>
+        <v>0.5230128067972385</v>
       </c>
       <c r="G50">
-        <v>-4.503001882639463</v>
+        <v>-7.258183544424673</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.013544386318628</v>
       </c>
       <c r="E51">
-        <v>-18.64518773491693</v>
+        <v>-21.54896300895937</v>
       </c>
       <c r="F51">
-        <v>0.6153517495547022</v>
+        <v>0.4433164073413008</v>
       </c>
       <c r="G51">
-        <v>-4.357076345813929</v>
+        <v>-7.664069669721478</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.887753961119604</v>
       </c>
       <c r="E52">
-        <v>-18.39775191513782</v>
+        <v>-20.63414786077385</v>
       </c>
       <c r="F52">
-        <v>0.7585499657418471</v>
+        <v>0.1869201288267979</v>
       </c>
       <c r="G52">
-        <v>-4.607840238777103</v>
+        <v>-7.694457167226448</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.794080970602235</v>
       </c>
       <c r="E53">
-        <v>-18.5582048061776</v>
+        <v>-20.79690121660952</v>
       </c>
       <c r="F53">
-        <v>0.5755793454440895</v>
+        <v>0.6378402678059032</v>
       </c>
       <c r="G53">
-        <v>-5.227551189909894</v>
+        <v>-7.6311694681522</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.723577409105869</v>
       </c>
       <c r="E54">
-        <v>-17.80019259898167</v>
+        <v>-20.199124533701</v>
       </c>
       <c r="F54">
-        <v>0.6625206462049117</v>
+        <v>0.170694896508164</v>
       </c>
       <c r="G54">
-        <v>-4.927615764051925</v>
+        <v>-7.218867505600288</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.66549809729093</v>
       </c>
       <c r="E55">
-        <v>-17.87793291227135</v>
+        <v>-20.86331581640601</v>
       </c>
       <c r="F55">
-        <v>0.4739254112421454</v>
+        <v>0.1632545004962188</v>
       </c>
       <c r="G55">
-        <v>-5.472409069631009</v>
+        <v>-7.053555414096782</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.616647770674033</v>
       </c>
       <c r="E56">
-        <v>-17.27891089901073</v>
+        <v>-20.37005178512052</v>
       </c>
       <c r="F56">
-        <v>0.2630007045695157</v>
+        <v>0.3326059323245498</v>
       </c>
       <c r="G56">
-        <v>-5.590694861749169</v>
+        <v>-8.198083839024696</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.565517262001857</v>
       </c>
       <c r="E57">
-        <v>-16.76134707620007</v>
+        <v>-19.30568831130569</v>
       </c>
       <c r="F57">
-        <v>0.3987784055623826</v>
+        <v>-0.02068199619320301</v>
       </c>
       <c r="G57">
-        <v>-5.564965301817953</v>
+        <v>-7.788688535456263</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.51576942346547</v>
       </c>
       <c r="E58">
-        <v>-17.13404048703134</v>
+        <v>-19.0081992683198</v>
       </c>
       <c r="F58">
-        <v>0.3784030525557232</v>
+        <v>0.1342218797629017</v>
       </c>
       <c r="G58">
-        <v>-6.448142709148103</v>
+        <v>-8.044924760195853</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.45777655047698</v>
       </c>
       <c r="E59">
-        <v>-15.7988561536618</v>
+        <v>-18.47450954956784</v>
       </c>
       <c r="F59">
-        <v>0.1819681484928624</v>
+        <v>-0.02734372684651663</v>
       </c>
       <c r="G59">
-        <v>-5.747561751581995</v>
+        <v>-8.684949218757612</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.398510401206514</v>
       </c>
       <c r="E60">
-        <v>-15.6872156839507</v>
+        <v>-18.55407936635661</v>
       </c>
       <c r="F60">
-        <v>0.4006911058954467</v>
+        <v>-0.03403030852191424</v>
       </c>
       <c r="G60">
-        <v>-6.080139156457178</v>
+        <v>-8.497628620509031</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.331794195484118</v>
       </c>
       <c r="E61">
-        <v>-15.97941546929563</v>
+        <v>-18.95587275116117</v>
       </c>
       <c r="F61">
-        <v>-0.07771095003893497</v>
+        <v>-0.251920756684685</v>
       </c>
       <c r="G61">
-        <v>-6.208052015003538</v>
+        <v>-8.078285127595089</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.264732908992431</v>
       </c>
       <c r="E62">
-        <v>-15.44055876170091</v>
+        <v>-18.57327103920112</v>
       </c>
       <c r="F62">
-        <v>0.121685367488934</v>
+        <v>-0.2574989827751369</v>
       </c>
       <c r="G62">
-        <v>-6.665715072534544</v>
+        <v>-7.891202888625335</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.196069930810126</v>
       </c>
       <c r="E63">
-        <v>-16.09061214855398</v>
+        <v>-17.33961962155755</v>
       </c>
       <c r="F63">
-        <v>0.02616218043510903</v>
+        <v>0.2012392877515901</v>
       </c>
       <c r="G63">
-        <v>-6.901319977473396</v>
+        <v>-8.66347039929882</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.131091051788908</v>
       </c>
       <c r="E64">
-        <v>-15.08827518322221</v>
+        <v>-17.85533582697308</v>
       </c>
       <c r="F64">
-        <v>-0.2632843007162886</v>
+        <v>-0.127211700928025</v>
       </c>
       <c r="G64">
-        <v>-7.375059044143103</v>
+        <v>-8.673355688279084</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.073100373084614</v>
       </c>
       <c r="E65">
-        <v>-14.41490921217766</v>
+        <v>-17.4735447118604</v>
       </c>
       <c r="F65">
-        <v>-0.2741740185934909</v>
+        <v>-0.1457870115684012</v>
       </c>
       <c r="G65">
-        <v>-7.161015722301524</v>
+        <v>-8.797511077638372</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.024122873307496</v>
       </c>
       <c r="E66">
-        <v>-14.61145404105857</v>
+        <v>-17.56454439704453</v>
       </c>
       <c r="F66">
-        <v>-0.3178472048038865</v>
+        <v>-0.2427068260633461</v>
       </c>
       <c r="G66">
-        <v>-6.726546346818653</v>
+        <v>-9.224137770738711</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.989349078820589</v>
       </c>
       <c r="E67">
-        <v>-15.24678988738671</v>
+        <v>-17.7026764397005</v>
       </c>
       <c r="F67">
-        <v>-0.2927592696427006</v>
+        <v>0.01334319487678668</v>
       </c>
       <c r="G67">
-        <v>-7.086369541482037</v>
+        <v>-8.843875267915864</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.965381937400611</v>
       </c>
       <c r="E68">
-        <v>-14.02543327667397</v>
+        <v>-18.01782653131631</v>
       </c>
       <c r="F68">
-        <v>-0.02910814941447958</v>
+        <v>-0.2129626377310243</v>
       </c>
       <c r="G68">
-        <v>-7.708325042490455</v>
+        <v>-8.869459163843352</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.957385211981943</v>
       </c>
       <c r="E69">
-        <v>-14.49840521593109</v>
+        <v>-18.30659826183743</v>
       </c>
       <c r="F69">
-        <v>-0.1831331275562141</v>
+        <v>-0.3178654288867481</v>
       </c>
       <c r="G69">
-        <v>-7.099062173079603</v>
+        <v>-9.432930567355005</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.957056655676014</v>
       </c>
       <c r="E70">
-        <v>-14.16121956979396</v>
+        <v>-18.03446414482049</v>
       </c>
       <c r="F70">
-        <v>-0.5156199222222684</v>
+        <v>-0.5616175073649193</v>
       </c>
       <c r="G70">
-        <v>-7.26978038544874</v>
+        <v>-8.205184959206433</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.967660248272568</v>
       </c>
       <c r="E71">
-        <v>-15.02195115290587</v>
+        <v>-17.75309646930191</v>
       </c>
       <c r="F71">
-        <v>-0.4579083936366297</v>
+        <v>-0.6434237585957874</v>
       </c>
       <c r="G71">
-        <v>-6.609528493642034</v>
+        <v>-8.56258483453507</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.978836747209976</v>
       </c>
       <c r="E72">
-        <v>-14.8284404016101</v>
+        <v>-17.96317237851773</v>
       </c>
       <c r="F72">
-        <v>-0.6448609760396445</v>
+        <v>-0.3213329748348668</v>
       </c>
       <c r="G72">
-        <v>-7.424227266492359</v>
+        <v>-8.371556425282506</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.989833070397305</v>
       </c>
       <c r="E73">
-        <v>-14.87367985694673</v>
+        <v>-17.53968307474242</v>
       </c>
       <c r="F73">
-        <v>-0.4515597858615742</v>
+        <v>-0.3865768482141614</v>
       </c>
       <c r="G73">
-        <v>-7.401437471000015</v>
+        <v>-8.926301230752639</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.990865530424485</v>
       </c>
       <c r="E74">
-        <v>-14.9915650923144</v>
+        <v>-18.92532819397944</v>
       </c>
       <c r="F74">
-        <v>-0.7778860121530087</v>
+        <v>-0.5796378118454198</v>
       </c>
       <c r="G74">
-        <v>-7.468631613810603</v>
+        <v>-8.548276656714341</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.977061950107081</v>
       </c>
       <c r="E75">
-        <v>-15.85092454780199</v>
+        <v>-18.54654398560785</v>
       </c>
       <c r="F75">
-        <v>-0.521426777715893</v>
+        <v>-0.5148677646205265</v>
       </c>
       <c r="G75">
-        <v>-6.765571057635581</v>
+        <v>-8.125629239352206</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.941458608527304</v>
       </c>
       <c r="E76">
-        <v>-16.48847028944587</v>
+        <v>-17.92364332890478</v>
       </c>
       <c r="F76">
-        <v>-0.5596766425401601</v>
+        <v>-0.6764043783708469</v>
       </c>
       <c r="G76">
-        <v>-6.939603126089528</v>
+        <v>-7.808091642861932</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.877952458606671</v>
       </c>
       <c r="E77">
-        <v>-15.79936334275066</v>
+        <v>-18.12614762957978</v>
       </c>
       <c r="F77">
-        <v>-0.4800929010510032</v>
+        <v>-0.9169258239781001</v>
       </c>
       <c r="G77">
-        <v>-6.888418781506856</v>
+        <v>-8.192902835255735</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.783805148449357</v>
       </c>
       <c r="E78">
-        <v>-16.91275207617252</v>
+        <v>-19.14406707397194</v>
       </c>
       <c r="F78">
-        <v>-0.5693793099291508</v>
+        <v>-0.8529609498687278</v>
       </c>
       <c r="G78">
-        <v>-6.183673157652345</v>
+        <v>-8.104210009713121</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.653511558314346</v>
       </c>
       <c r="E79">
-        <v>-16.62178856423169</v>
+        <v>-20.19161632379629</v>
       </c>
       <c r="F79">
-        <v>-0.8280892185996728</v>
+        <v>-0.8601321264747632</v>
       </c>
       <c r="G79">
-        <v>-6.52732764790193</v>
+        <v>-7.617076475791523</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.489875526277704</v>
       </c>
       <c r="E80">
-        <v>-17.4916721933131</v>
+        <v>-20.56455427222397</v>
       </c>
       <c r="F80">
-        <v>-1.046537158024528</v>
+        <v>-0.934882344168585</v>
       </c>
       <c r="G80">
-        <v>-6.163568214592352</v>
+        <v>-8.261782045745813</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.290517494400373</v>
       </c>
       <c r="E81">
-        <v>-18.90073405164378</v>
+        <v>-20.23587762874725</v>
       </c>
       <c r="F81">
-        <v>-0.6382497757979017</v>
+        <v>-0.7771355112860724</v>
       </c>
       <c r="G81">
-        <v>-6.405089064409881</v>
+        <v>-7.680781303603719</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.064085884413956</v>
       </c>
       <c r="E82">
-        <v>-19.13476558836018</v>
+        <v>-21.953161013462</v>
       </c>
       <c r="F82">
-        <v>-1.112225036331723</v>
+        <v>-1.242866859427233</v>
       </c>
       <c r="G82">
-        <v>-5.942834280215906</v>
+        <v>-7.243941577514728</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.813351673172272</v>
       </c>
       <c r="E83">
-        <v>-20.26957853231234</v>
+        <v>-21.76804152450244</v>
       </c>
       <c r="F83">
-        <v>-0.8991705970664955</v>
+        <v>-1.228323212936282</v>
       </c>
       <c r="G83">
-        <v>-5.543397097629601</v>
+        <v>-6.854873023557421</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.550268008381259</v>
       </c>
       <c r="E84">
-        <v>-21.33089887159401</v>
+        <v>-22.95104648884422</v>
       </c>
       <c r="F84">
-        <v>-0.4967778772781908</v>
+        <v>-1.070478632700239</v>
       </c>
       <c r="G84">
-        <v>-6.143049453339948</v>
+        <v>-6.884439505768652</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.282301144100722</v>
       </c>
       <c r="E85">
-        <v>-21.22724663003244</v>
+        <v>-23.45239384623341</v>
       </c>
       <c r="F85">
-        <v>-0.725210957376391</v>
+        <v>-1.059093551116163</v>
       </c>
       <c r="G85">
-        <v>-5.593260534542104</v>
+        <v>-6.949167292152483</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.021927238786313</v>
       </c>
       <c r="E86">
-        <v>-22.9952534521071</v>
+        <v>-24.13929542608689</v>
       </c>
       <c r="F86">
-        <v>-0.9906687469101177</v>
+        <v>-1.210949863397368</v>
       </c>
       <c r="G86">
-        <v>-5.621473003627773</v>
+        <v>-6.880284771116867</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.77945681788995</v>
       </c>
       <c r="E87">
-        <v>-24.68911556925418</v>
+        <v>-25.27942479852404</v>
       </c>
       <c r="F87">
-        <v>-0.9073507251691406</v>
+        <v>-1.395339477056121</v>
       </c>
       <c r="G87">
-        <v>-5.717068316619768</v>
+        <v>-7.451827284653262</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.565113806126857</v>
       </c>
       <c r="E88">
-        <v>-24.75255496162763</v>
+        <v>-26.54829868699927</v>
       </c>
       <c r="F88">
-        <v>-0.896995304266744</v>
+        <v>-1.164500818020191</v>
       </c>
       <c r="G88">
-        <v>-5.539487343347722</v>
+        <v>-6.570530267189419</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.389554770901549</v>
       </c>
       <c r="E89">
-        <v>-26.20868125032003</v>
+        <v>-28.57214617661128</v>
       </c>
       <c r="F89">
-        <v>-0.9574752367125388</v>
+        <v>-1.179689762717923</v>
       </c>
       <c r="G89">
-        <v>-5.426862584101716</v>
+        <v>-6.976005884839354</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.257415316820882</v>
       </c>
       <c r="E90">
-        <v>-28.31084869789469</v>
+        <v>-29.69127475083786</v>
       </c>
       <c r="F90">
-        <v>-0.8581283057273912</v>
+        <v>-1.370432125988746</v>
       </c>
       <c r="G90">
-        <v>-5.664649138550948</v>
+        <v>-6.806181519765821</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.177066313931023</v>
       </c>
       <c r="E91">
-        <v>-29.81370430987224</v>
+        <v>-30.79051653145977</v>
       </c>
       <c r="F91">
-        <v>-0.5498281824882768</v>
+        <v>-1.4235619544695</v>
       </c>
       <c r="G91">
-        <v>-5.251122274149505</v>
+        <v>-6.882840512273185</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.145831850445243</v>
       </c>
       <c r="E92">
-        <v>-31.6642470992107</v>
+        <v>-32.59207708169426</v>
       </c>
       <c r="F92">
-        <v>-0.9137962519303235</v>
+        <v>-1.304002030488642</v>
       </c>
       <c r="G92">
-        <v>-4.350011641633124</v>
+        <v>-7.448298243108399</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.168071599519563</v>
       </c>
       <c r="E93">
-        <v>-33.55287888342767</v>
+        <v>-34.13735317393866</v>
       </c>
       <c r="F93">
-        <v>-0.9075735560004937</v>
+        <v>-1.664881946253052</v>
       </c>
       <c r="G93">
-        <v>-5.327916999023979</v>
+        <v>-7.084909590899219</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.236087940801611</v>
       </c>
       <c r="E94">
-        <v>-34.56731366707093</v>
+        <v>-34.75142104208977</v>
       </c>
       <c r="F94">
-        <v>-0.8251551412589568</v>
+        <v>-1.191047508177707</v>
       </c>
       <c r="G94">
-        <v>-5.656551544161891</v>
+        <v>-7.4571076047884</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.347905620614237</v>
       </c>
       <c r="E95">
-        <v>-36.61025773157328</v>
+        <v>-37.74759756402172</v>
       </c>
       <c r="F95">
-        <v>-0.9761855712395712</v>
+        <v>-1.669124844090191</v>
       </c>
       <c r="G95">
-        <v>-6.024293563755212</v>
+        <v>-7.501899285934739</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.499358924503225</v>
       </c>
       <c r="E96">
-        <v>-37.61001573095768</v>
+        <v>-40.05147003660903</v>
       </c>
       <c r="F96">
-        <v>-1.173423991683147</v>
+        <v>-1.793548941460288</v>
       </c>
       <c r="G96">
-        <v>-5.694718823684148</v>
+        <v>-7.678543374819172</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.681882767092298</v>
       </c>
       <c r="E97">
-        <v>-40.67276308503938</v>
+        <v>-40.89176914499833</v>
       </c>
       <c r="F97">
-        <v>-1.420800177548567</v>
+        <v>-1.900310589067894</v>
       </c>
       <c r="G97">
-        <v>-6.254939271476236</v>
+        <v>-7.815798592877354</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.903916576650778</v>
       </c>
       <c r="E98">
-        <v>-43.64623383829686</v>
+        <v>-43.66743615360078</v>
       </c>
       <c r="F98">
-        <v>-1.124141929788396</v>
+        <v>-1.873357170515604</v>
       </c>
       <c r="G98">
-        <v>-5.76575319932029</v>
+        <v>-7.443259592797629</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.148703861787217</v>
       </c>
       <c r="E99">
-        <v>-45.6963147778353</v>
+        <v>-45.45529806996206</v>
       </c>
       <c r="F99">
-        <v>-1.167135026361094</v>
+        <v>-1.941367791020249</v>
       </c>
       <c r="G99">
-        <v>-6.419956724426748</v>
+        <v>-8.255770095046495</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.446243791423477</v>
       </c>
       <c r="E100">
-        <v>-46.06093165527389</v>
+        <v>-48.02029141077967</v>
       </c>
       <c r="F100">
-        <v>-0.8825477483945179</v>
+        <v>-2.420893113152827</v>
       </c>
       <c r="G100">
-        <v>-6.20650267969116</v>
+        <v>-8.819744701480117</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.752625218215248</v>
       </c>
       <c r="E101">
-        <v>-48.38560567321544</v>
+        <v>-49.20283786712817</v>
       </c>
       <c r="F101">
-        <v>-1.736818199879564</v>
+        <v>-2.517949608269233</v>
       </c>
       <c r="G101">
-        <v>-7.039230683548356</v>
+        <v>-8.480039692058883</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.141477151165342</v>
       </c>
       <c r="E102">
-        <v>-51.48474950501529</v>
+        <v>-51.65235625286868</v>
       </c>
       <c r="F102">
-        <v>-1.797626165816867</v>
+        <v>-2.936820212434026</v>
       </c>
       <c r="G102">
-        <v>-7.108603165323783</v>
+        <v>-9.016053430867819</v>
       </c>
     </row>
   </sheetData>
